--- a/itemCreation/newpart/excel_files/NewPartNumber_Form.xlsx
+++ b/itemCreation/newpart/excel_files/NewPartNumber_Form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reliablesprinkler-my.sharepoint.com/personal/btrent_reliablesprinkler_com/Documents/Documents/GitHub/reliable-PIM/itemCreation/newpart/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7317" documentId="13_ncr:1_{6D8B5FBB-8782-4E9C-BAB6-1DB9047B74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AB04E3-38C8-4239-8305-117D2568A274}"/>
+  <xr:revisionPtr revIDLastSave="7349" documentId="13_ncr:1_{6D8B5FBB-8782-4E9C-BAB6-1DB9047B74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39379A15-6204-4F5A-8504-BC1A1A1070FE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1365" windowWidth="29040" windowHeight="15720" xr2:uid="{4EF26F20-0A39-4FC5-A8F1-8CFAC06D9054}"/>
+    <workbookView xWindow="4155" yWindow="2430" windowWidth="21600" windowHeight="11055" xr2:uid="{4EF26F20-0A39-4FC5-A8F1-8CFAC06D9054}"/>
   </bookViews>
   <sheets>
     <sheet name="newPart" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>New Part Number Form</t>
   </si>
@@ -83,49 +83,25 @@
     <t>Name</t>
   </si>
   <si>
-    <t>VENDOR NAME</t>
-  </si>
-  <si>
     <t>Item Category Search</t>
   </si>
   <si>
-    <t>BUYER OR SALESMAN REQUEST</t>
-  </si>
-  <si>
-    <t>PRODUCT GROUP ID</t>
-  </si>
-  <si>
-    <t>COPS GROUP ID</t>
-  </si>
-  <si>
-    <t>TEST PRODUCT</t>
-  </si>
-  <si>
-    <t>SITE ID</t>
-  </si>
-  <si>
-    <t>VENDOR ID</t>
-  </si>
-  <si>
-    <t>EXTERNAL ID</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>WH</t>
-  </si>
-  <si>
-    <t>WD</t>
-  </si>
-  <si>
-    <t>PURCH PRICE</t>
-  </si>
-  <si>
-    <t>DESCRIPTION LIKE '%%'</t>
+    <t>DALLAS</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>BBSC100</t>
+  </si>
+  <si>
+    <t>MILWAUKEE</t>
+  </si>
+  <si>
+    <t>175 SW</t>
+  </si>
+  <si>
+    <t>USVA0004081</t>
   </si>
 </sst>
 </file>
@@ -133,7 +109,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -164,14 +140,12 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -219,9 +193,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -236,6 +207,9 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,129 +538,125 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="78.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="B15" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -698,6 +668,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010041DA5353F392A748A2A17B8DB6FF9B3D" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9f03a5888bd8c5960d4fff49bf74d24">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31f32cf4-ad1a-4b4a-95ab-52184a0a8224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef95c939d6d143fc94d9138611b38544" ns2:_="">
     <xsd:import namespace="31f32cf4-ad1a-4b4a-95ab-52184a0a8224"/>
@@ -841,22 +820,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FC5F73-F8FF-462E-B5C4-933FD6EC0A50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7269E01-7163-412E-BCE4-E087D8BB6E17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -874,7 +852,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270F0DD1-07F6-4995-AC82-89806E86ACAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -888,12 +866,4 @@
     <ds:schemaRef ds:uri="31f32cf4-ad1a-4b4a-95ab-52184a0a8224"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FC5F73-F8FF-462E-B5C4-933FD6EC0A50}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/itemCreation/newpart/excel_files/NewPartNumber_Form.xlsx
+++ b/itemCreation/newpart/excel_files/NewPartNumber_Form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reliablesprinkler-my.sharepoint.com/personal/btrent_reliablesprinkler_com/Documents/Documents/GitHub/reliable-PIM/itemCreation/newpart/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7349" documentId="13_ncr:1_{6D8B5FBB-8782-4E9C-BAB6-1DB9047B74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39379A15-6204-4F5A-8504-BC1A1A1070FE}"/>
+  <xr:revisionPtr revIDLastSave="7406" documentId="13_ncr:1_{6D8B5FBB-8782-4E9C-BAB6-1DB9047B74BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4182F127-5A01-42B2-8482-FD5C431F4996}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="2430" windowWidth="21600" windowHeight="11055" xr2:uid="{4EF26F20-0A39-4FC5-A8F1-8CFAC06D9054}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{4EF26F20-0A39-4FC5-A8F1-8CFAC06D9054}"/>
   </bookViews>
   <sheets>
     <sheet name="newPart" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>New Part Number Form</t>
   </si>
@@ -80,28 +80,31 @@
     <t>Item SKU</t>
   </si>
   <si>
+    <t>Item Category Code</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Item Category Search</t>
-  </si>
-  <si>
-    <t>DALLAS</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>BBSC100</t>
-  </si>
-  <si>
-    <t>MILWAUKEE</t>
-  </si>
-  <si>
-    <t>175 SW</t>
-  </si>
-  <si>
-    <t>USVA0004081</t>
+    <t> GENERAL</t>
+  </si>
+  <si>
+    <t> APD10</t>
+  </si>
+  <si>
+    <t> DAPV500B-2  </t>
+  </si>
+  <si>
+    <t> MODEL DAP500B-2, 208V</t>
+  </si>
+  <si>
+    <t> SEATTLE</t>
+  </si>
+  <si>
+    <t> KIMBERLY BAILEY</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
   </si>
 </sst>
 </file>
@@ -535,35 +538,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE31D1C-BC57-4204-A988-BB335C5DF60C}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="48" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -571,88 +574,80 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10608</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -668,6 +663,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -676,7 +677,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010041DA5353F392A748A2A17B8DB6FF9B3D" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9f03a5888bd8c5960d4fff49bf74d24">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31f32cf4-ad1a-4b4a-95ab-52184a0a8224" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef95c939d6d143fc94d9138611b38544" ns2:_="">
     <xsd:import namespace="31f32cf4-ad1a-4b4a-95ab-52184a0a8224"/>
@@ -820,13 +821,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270F0DD1-07F6-4995-AC82-89806E86ACAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="31f32cf4-ad1a-4b4a-95ab-52184a0a8224"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FC5F73-F8FF-462E-B5C4-933FD6EC0A50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -834,7 +845,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7269E01-7163-412E-BCE4-E087D8BB6E17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -850,20 +861,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270F0DD1-07F6-4995-AC82-89806E86ACAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="31f32cf4-ad1a-4b4a-95ab-52184a0a8224"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>